--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484226_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484226_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.4415</v>
+        <v>4.4181</v>
       </c>
       <c r="E2" t="n">
-        <v>2.6201</v>
+        <v>3.6512</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8214</v>
+        <v>0.7669</v>
       </c>
       <c r="G2" t="n">
         <v>2.2417</v>
@@ -610,13 +610,13 @@
         <v>2.7348</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.5661</v>
+        <v>-0.5895</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.5226</v>
+        <v>0.5085</v>
       </c>
       <c r="U2" t="n">
-        <v>-1.0435</v>
+        <v>-1.098</v>
       </c>
       <c r="V2" t="n">
         <v>1.0078</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.1049</v>
+        <v>-0.6548</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.5594</v>
+        <v>-1.409</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4546</v>
+        <v>0.7541</v>
       </c>
       <c r="G3" t="n">
         <v>-3.0775</v>
@@ -688,13 +688,13 @@
         <v>2.3441</v>
       </c>
       <c r="S3" t="n">
-        <v>1.328</v>
+        <v>0.778</v>
       </c>
       <c r="T3" t="n">
-        <v>2.3692</v>
+        <v>1.5196</v>
       </c>
       <c r="U3" t="n">
-        <v>-1.0412</v>
+        <v>-0.7416</v>
       </c>
       <c r="V3" t="n">
         <v>0.2772</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>G. GARCÍA RIERA</t>
+          <t>S. LLUFRIU ARCOS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.9022</v>
+        <v>-1.4413</v>
       </c>
       <c r="E4" t="n">
-        <v>1.1527</v>
+        <v>0.8583</v>
       </c>
       <c r="F4" t="n">
-        <v>-2.0549</v>
+        <v>-2.2996</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.3519</v>
+        <v>-1.5546</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.9739</v>
+        <v>-2.3367</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.378</v>
+        <v>0.7821</v>
       </c>
       <c r="J4" t="n">
-        <v>0.6454</v>
+        <v>0.5077</v>
       </c>
       <c r="K4" t="n">
-        <v>0.6178</v>
+        <v>-0.8148</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0276</v>
+        <v>1.3225</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.9973</v>
+        <v>-2.0623</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.5917</v>
+        <v>-1.5219</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.4056</v>
+        <v>-0.5405</v>
       </c>
       <c r="P4" t="n">
-        <v>0.3907</v>
+        <v>2.5395</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.3674</v>
+        <v>2.5395</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3247</v>
+        <v>-0.5433</v>
       </c>
       <c r="T4" t="n">
-        <v>1.8161</v>
+        <v>0.7375</v>
       </c>
       <c r="U4" t="n">
-        <v>-1.4914</v>
+        <v>-1.2809</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.2657</v>
+        <v>-1.8828</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.3321</v>
+        <v>-0.3869</v>
       </c>
       <c r="X4" t="n">
-        <v>0.0664</v>
+        <v>-1.4959</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S. LLUFRIU ARCOS</t>
+          <t>G. GARCÍA RIERA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.9396</v>
+        <v>-2.0144</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3328</v>
+        <v>0.0405</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.2724</v>
+        <v>-2.0549</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.5546</v>
+        <v>-1.3519</v>
       </c>
       <c r="H5" t="n">
-        <v>-2.3367</v>
+        <v>-0.9739</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7821</v>
+        <v>-0.378</v>
       </c>
       <c r="J5" t="n">
-        <v>0.5077</v>
+        <v>0.6454</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.8148</v>
+        <v>0.6178</v>
       </c>
       <c r="L5" t="n">
-        <v>1.3225</v>
+        <v>0.0276</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.0623</v>
+        <v>-1.9973</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.5219</v>
+        <v>-1.5917</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.5405</v>
+        <v>-0.4056</v>
       </c>
       <c r="P5" t="n">
-        <v>2.5395</v>
+        <v>0.3907</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R5" t="n">
-        <v>2.5395</v>
+        <v>1.3674</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.0416</v>
+        <v>-0.7875</v>
       </c>
       <c r="T5" t="n">
-        <v>0.212</v>
+        <v>0.7038</v>
       </c>
       <c r="U5" t="n">
-        <v>-1.2537</v>
+        <v>-1.4914</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.8828</v>
+        <v>-0.2657</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.3869</v>
+        <v>-0.3321</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.4959</v>
+        <v>0.0664</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-2.6076</v>
+        <v>-2.9145</v>
       </c>
       <c r="E6" t="n">
-        <v>0.965</v>
+        <v>0.9849</v>
       </c>
       <c r="F6" t="n">
-        <v>-3.5726</v>
+        <v>-3.8994</v>
       </c>
       <c r="G6" t="n">
         <v>-1.0361</v>
@@ -922,13 +922,13 @@
         <v>1.5627</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.0639</v>
+        <v>-0.3708</v>
       </c>
       <c r="T6" t="n">
-        <v>0.9604</v>
+        <v>0.9804</v>
       </c>
       <c r="U6" t="n">
-        <v>-1.0243</v>
+        <v>-1.3511</v>
       </c>
       <c r="V6" t="n">
         <v>-2.0936</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-4.495</v>
+        <v>-3.8939</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.0888</v>
+        <v>-1.6239</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.4062</v>
+        <v>-2.27</v>
       </c>
       <c r="G7" t="n">
         <v>-1.63</v>
@@ -1000,13 +1000,13 @@
         <v>1.3674</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.9232</v>
+        <v>-1.322</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1457</v>
+        <v>0.3193</v>
       </c>
       <c r="U7" t="n">
-        <v>-1.7775</v>
+        <v>-1.6413</v>
       </c>
       <c r="V7" t="n">
         <v>0.6209</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-4.8248</v>
+        <v>-4.3265</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.4421</v>
+        <v>-0.9166</v>
       </c>
       <c r="F8" t="n">
-        <v>-3.3827</v>
+        <v>-3.4099</v>
       </c>
       <c r="G8" t="n">
         <v>-1.7545</v>
@@ -1078,13 +1078,13 @@
         <v>1.7581</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.8038</v>
+        <v>-1.3055</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3548</v>
+        <v>0.1707</v>
       </c>
       <c r="U8" t="n">
-        <v>-1.449</v>
+        <v>-1.4762</v>
       </c>
       <c r="V8" t="n">
         <v>2.8358</v>
@@ -1111,10 +1111,10 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-11.4326</v>
+        <v>-10.8273</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9802999999999997</v>
+        <v>1.5854</v>
       </c>
       <c r="F9" t="n">
         <v>-12.4128</v>
@@ -1147,7 +1147,7 @@
         <v>-2.7042</v>
       </c>
       <c r="P9" t="n">
-        <v>0.9768000000000008</v>
+        <v>0.976799999999999</v>
       </c>
       <c r="Q9" t="n">
         <v>-12.6972</v>
@@ -1156,13 +1156,13 @@
         <v>13.674</v>
       </c>
       <c r="S9" t="n">
-        <v>-4.7459</v>
+        <v>-4.1406</v>
       </c>
       <c r="T9" t="n">
-        <v>4.334600000000001</v>
+        <v>4.939800000000001</v>
       </c>
       <c r="U9" t="n">
-        <v>-9.0806</v>
+        <v>-9.080500000000001</v>
       </c>
       <c r="V9" t="n">
         <v>0.4996</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>8.536799999999999</v>
+        <v>9.8499</v>
       </c>
       <c r="E10" t="n">
-        <v>8.469099999999999</v>
+        <v>9.7836</v>
       </c>
       <c r="F10" t="n">
-        <v>0.06759999999999999</v>
+        <v>0.0663</v>
       </c>
       <c r="G10" t="n">
         <v>10.0188</v>
@@ -1234,13 +1234,13 @@
         <v>1.7581</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.7127</v>
+        <v>0.6004</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.0659</v>
+        <v>1.2485</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.6468</v>
+        <v>-0.6481</v>
       </c>
       <c r="V10" t="n">
         <v>-1.5507</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>7.9398</v>
+        <v>6.1133</v>
       </c>
       <c r="E11" t="n">
-        <v>7.8976</v>
+        <v>5.7742</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0423</v>
+        <v>0.3392</v>
       </c>
       <c r="G11" t="n">
         <v>3.4634</v>
@@ -1312,13 +1312,13 @@
         <v>0.586</v>
       </c>
       <c r="S11" t="n">
-        <v>4.203</v>
+        <v>2.3765</v>
       </c>
       <c r="T11" t="n">
-        <v>4.5042</v>
+        <v>2.3807</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3012</v>
+        <v>-0.0043</v>
       </c>
       <c r="V11" t="n">
         <v>0.6642</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>2.5168</v>
+        <v>2.9032</v>
       </c>
       <c r="E12" t="n">
-        <v>3.758</v>
+        <v>3.6569</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.2412</v>
+        <v>-0.7537</v>
       </c>
       <c r="G12" t="n">
         <v>-0.353</v>
@@ -1390,13 +1390,13 @@
         <v>1.7581</v>
       </c>
       <c r="S12" t="n">
-        <v>0.2801</v>
+        <v>0.6665</v>
       </c>
       <c r="T12" t="n">
-        <v>1.761</v>
+        <v>1.6599</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.4809</v>
+        <v>-0.9933999999999999</v>
       </c>
       <c r="V12" t="n">
         <v>0.8317</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>C. VIDAL AGRA</t>
+          <t>A. SIMON</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>1.5631</v>
+        <v>1.661</v>
       </c>
       <c r="E13" t="n">
-        <v>0.2512</v>
+        <v>1.993</v>
       </c>
       <c r="F13" t="n">
-        <v>1.3119</v>
+        <v>-0.332</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.1235</v>
+        <v>0.2981</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.2985</v>
+        <v>1.0269</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1751</v>
+        <v>-0.7288</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.2435</v>
+        <v>0.9375</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.284</v>
+        <v>1.3955</v>
       </c>
       <c r="L13" t="n">
-        <v>0.0405</v>
+        <v>-0.458</v>
       </c>
       <c r="M13" t="n">
-        <v>0.1201</v>
+        <v>-0.6394</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.0146</v>
+        <v>-0.3686</v>
       </c>
       <c r="O13" t="n">
-        <v>0.1346</v>
+        <v>-0.2708</v>
       </c>
       <c r="P13" t="n">
-        <v>0.586</v>
+        <v>-0.7814</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.9767</v>
+        <v>-2.9301</v>
       </c>
       <c r="R13" t="n">
-        <v>1.5627</v>
+        <v>2.1488</v>
       </c>
       <c r="S13" t="n">
-        <v>0.4364</v>
+        <v>0.5935</v>
       </c>
       <c r="T13" t="n">
-        <v>1.1942</v>
+        <v>0.9389999999999999</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.7578</v>
+        <v>-0.3455</v>
       </c>
       <c r="V13" t="n">
-        <v>0.6642</v>
+        <v>1.5507</v>
       </c>
       <c r="W13" t="n">
-        <v>0.2772</v>
+        <v>3.0466</v>
       </c>
       <c r="X13" t="n">
-        <v>0.3869</v>
+        <v>-1.4959</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. SIMON</t>
+          <t>C. VIDAL AGRA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.8197</v>
+        <v>0.8826000000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>1.2852</v>
+        <v>-0.4566</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.4655</v>
+        <v>1.3392</v>
       </c>
       <c r="G14" t="n">
-        <v>0.2981</v>
+        <v>-0.1235</v>
       </c>
       <c r="H14" t="n">
-        <v>1.0269</v>
+        <v>-0.2985</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.7288</v>
+        <v>0.1751</v>
       </c>
       <c r="J14" t="n">
-        <v>0.9375</v>
+        <v>-0.2435</v>
       </c>
       <c r="K14" t="n">
-        <v>1.3955</v>
+        <v>-0.284</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.458</v>
+        <v>0.0405</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.6394</v>
+        <v>0.1201</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.3686</v>
+        <v>-0.0146</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.2708</v>
+        <v>0.1346</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.7814</v>
+        <v>0.586</v>
       </c>
       <c r="Q14" t="n">
-        <v>-2.9301</v>
+        <v>-0.9767</v>
       </c>
       <c r="R14" t="n">
-        <v>2.1488</v>
+        <v>1.5627</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.2477</v>
+        <v>-0.2442</v>
       </c>
       <c r="T14" t="n">
-        <v>0.2312</v>
+        <v>0.4864</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.479</v>
+        <v>-0.7306</v>
       </c>
       <c r="V14" t="n">
-        <v>1.5507</v>
+        <v>0.6642</v>
       </c>
       <c r="W14" t="n">
-        <v>3.0466</v>
+        <v>0.2772</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.4959</v>
+        <v>0.3869</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. LAJAY BOBEPARI</t>
+          <t>À. RIERA PERETÓ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2109</v>
+        <v>0.0572</v>
       </c>
       <c r="E15" t="n">
-        <v>0.3797</v>
+        <v>-1.0327</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.1688</v>
+        <v>1.0899</v>
       </c>
       <c r="G15" t="n">
-        <v>0.738</v>
+        <v>-0.7752</v>
       </c>
       <c r="H15" t="n">
-        <v>1.1292</v>
+        <v>-0.5054999999999999</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.3912</v>
+        <v>-0.2696</v>
       </c>
       <c r="J15" t="n">
-        <v>1.0179</v>
+        <v>-1.4944</v>
       </c>
       <c r="K15" t="n">
-        <v>1.0041</v>
+        <v>-0.2814</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0138</v>
+        <v>-1.213</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.2799</v>
+        <v>0.7193000000000001</v>
       </c>
       <c r="N15" t="n">
-        <v>0.1251</v>
+        <v>-0.2241</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.4051</v>
+        <v>0.9433</v>
       </c>
       <c r="P15" t="n">
-        <v>-1.5627</v>
+        <v>0.586</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.9534</v>
+        <v>-0.9767</v>
       </c>
       <c r="R15" t="n">
-        <v>0.3907</v>
+        <v>1.5627</v>
       </c>
       <c r="S15" t="n">
-        <v>1.3129</v>
+        <v>0.8557</v>
       </c>
       <c r="T15" t="n">
-        <v>1.3152</v>
+        <v>1.1612</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0023</v>
+        <v>-0.3055</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.2772</v>
+        <v>-0.6093</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.2772</v>
+        <v>-0.8865</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>À. RIERA PERETÓ</t>
+          <t>A. LAJAY BOBEPARI</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.1349</v>
+        <v>-0.0393</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.6282</v>
+        <v>0.0764</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7631</v>
+        <v>-0.1157</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.7752</v>
+        <v>0.738</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.5054999999999999</v>
+        <v>1.1292</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.2696</v>
+        <v>-0.3912</v>
       </c>
       <c r="J16" t="n">
-        <v>-1.4944</v>
+        <v>1.0179</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.2814</v>
+        <v>1.0041</v>
       </c>
       <c r="L16" t="n">
-        <v>-1.213</v>
+        <v>0.0138</v>
       </c>
       <c r="M16" t="n">
-        <v>0.7193000000000001</v>
+        <v>-0.2799</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.2241</v>
+        <v>0.1251</v>
       </c>
       <c r="O16" t="n">
-        <v>0.9433</v>
+        <v>-0.4051</v>
       </c>
       <c r="P16" t="n">
-        <v>0.586</v>
+        <v>-1.5627</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.9767</v>
+        <v>-1.9534</v>
       </c>
       <c r="R16" t="n">
-        <v>1.5627</v>
+        <v>0.3907</v>
       </c>
       <c r="S16" t="n">
-        <v>0.9333</v>
+        <v>1.0627</v>
       </c>
       <c r="T16" t="n">
-        <v>1.5657</v>
+        <v>1.0119</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.6324</v>
+        <v>0.0508</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.6093</v>
+        <v>-0.2772</v>
       </c>
       <c r="W16" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.8865</v>
+        <v>-0.2772</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.6178</v>
+        <v>-0.1824</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.1084</v>
+        <v>0.5995</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.5095</v>
+        <v>-0.7818000000000001</v>
       </c>
       <c r="G17" t="n">
         <v>1.1285</v>
@@ -1780,13 +1780,13 @@
         <v>0.7814</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.0551</v>
+        <v>0.3804</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.4099</v>
+        <v>0.2979</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3548</v>
+        <v>0.0824</v>
       </c>
       <c r="V17" t="n">
         <v>-1.4959</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-4.3804</v>
+        <v>-3.7049</v>
       </c>
       <c r="E18" t="n">
-        <v>-3.4121</v>
+        <v>-3.0076</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.9683</v>
+        <v>-0.6973</v>
       </c>
       <c r="G18" t="n">
         <v>-2.6917</v>
@@ -1858,13 +1858,13 @@
         <v>1.3674</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.8254</v>
+        <v>-0.15</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.4099</v>
+        <v>-0.0054</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.4155</v>
+        <v>-0.1445</v>
       </c>
       <c r="V18" t="n">
         <v>-0.2772</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-5.2913</v>
+        <v>-4.7599</v>
       </c>
       <c r="E19" t="n">
-        <v>-5.4794</v>
+        <v>-4.9738</v>
       </c>
       <c r="F19" t="n">
-        <v>0.188</v>
+        <v>0.2139</v>
       </c>
       <c r="G19" t="n">
         <v>-3.5403</v>
@@ -1936,13 +1936,13 @@
         <v>0.7814</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.5789</v>
+        <v>-0.0475</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.6052</v>
+        <v>-0.0997</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0263</v>
+        <v>0.0522</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>11.4325</v>
+        <v>12.7807</v>
       </c>
       <c r="E20" t="n">
-        <v>12.4127</v>
+        <v>12.4129</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.9804000000000002</v>
+        <v>0.3679999999999999</v>
       </c>
       <c r="G20" t="n">
         <v>8.163100000000002</v>
@@ -1984,7 +1984,7 @@
         <v>5.4657</v>
       </c>
       <c r="I20" t="n">
-        <v>2.697399999999999</v>
+        <v>2.6974</v>
       </c>
       <c r="J20" t="n">
         <v>11.4097</v>
@@ -2002,10 +2002,10 @@
         <v>-3.2399</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.006999999999999784</v>
+        <v>-0.007000000000000006</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.9767000000000002</v>
+        <v>-0.9767</v>
       </c>
       <c r="Q20" t="n">
         <v>-13.6738</v>
@@ -2014,19 +2014,19 @@
         <v>12.6973</v>
       </c>
       <c r="S20" t="n">
-        <v>4.7459</v>
+        <v>6.094</v>
       </c>
       <c r="T20" t="n">
-        <v>9.0806</v>
+        <v>9.080399999999999</v>
       </c>
       <c r="U20" t="n">
-        <v>-4.3348</v>
+        <v>-2.986499999999999</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.4995000000000001</v>
+        <v>-0.4994999999999997</v>
       </c>
       <c r="W20" t="n">
-        <v>5.596400000000001</v>
+        <v>5.5964</v>
       </c>
       <c r="X20" t="n">
         <v>-6.096099999999999</v>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484226_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484226_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X20"/>
+  <dimension ref="A1:Y22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,11 +632,16 @@
       <c r="X2" t="n">
         <v>0.4533</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_2484226_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M. CORBERA BUSQUETA</t>
+          <t>G. GARCÍA RIERA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +653,78 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.6548</v>
+        <v>1.214</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.409</v>
+        <v>1.214</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7541</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>-3.0775</v>
+        <v>1.214</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.9606</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>-2.1169</v>
+        <v>1.214</v>
       </c>
       <c r="J3" t="n">
-        <v>-2.2291</v>
+        <v>1.214</v>
       </c>
       <c r="K3" t="n">
-        <v>0.2916</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>-2.5207</v>
+        <v>1.214</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.8484</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.2522</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>0.4039</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>1.3674</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.3441</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>0.778</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>1.5196</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.7416</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_2484226_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>S. LLUFRIU ARCOS</t>
+          <t>M. CORBERA BUSQUETA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +736,78 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-1.4413</v>
+        <v>-0.6548</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8583</v>
+        <v>-1.409</v>
       </c>
       <c r="F4" t="n">
-        <v>-2.2996</v>
+        <v>0.7541</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.5546</v>
+        <v>-3.0775</v>
       </c>
       <c r="H4" t="n">
-        <v>-2.3367</v>
+        <v>-0.9606</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7821</v>
+        <v>-2.1169</v>
       </c>
       <c r="J4" t="n">
-        <v>0.5077</v>
+        <v>-2.2291</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.8148</v>
+        <v>0.2916</v>
       </c>
       <c r="L4" t="n">
-        <v>1.3225</v>
+        <v>-2.5207</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.0623</v>
+        <v>-0.8484</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.5219</v>
+        <v>-1.2522</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.5405</v>
+        <v>0.4039</v>
       </c>
       <c r="P4" t="n">
-        <v>2.5395</v>
+        <v>1.3674</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R4" t="n">
-        <v>2.5395</v>
+        <v>2.3441</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.5433</v>
+        <v>0.778</v>
       </c>
       <c r="T4" t="n">
-        <v>0.7375</v>
+        <v>1.5196</v>
       </c>
       <c r="U4" t="n">
-        <v>-1.2809</v>
+        <v>-0.7416</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.8828</v>
+        <v>0.2772</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.3869</v>
+        <v>0.2772</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.4959</v>
+        <v>0</v>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_2484226_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>G. GARCÍA RIERA</t>
+          <t>S. LLUFRIU ARCOS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +819,72 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-2.0144</v>
+        <v>-1.4413</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0405</v>
+        <v>0.8583</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.0549</v>
+        <v>-2.2996</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.3519</v>
+        <v>-1.5546</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.9739</v>
+        <v>-2.3367</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.378</v>
+        <v>0.7821</v>
       </c>
       <c r="J5" t="n">
-        <v>0.6454</v>
+        <v>0.5077</v>
       </c>
       <c r="K5" t="n">
-        <v>0.6178</v>
+        <v>-0.8148</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0276</v>
+        <v>1.3225</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.9973</v>
+        <v>-2.0623</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.5917</v>
+        <v>-1.5219</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.4056</v>
+        <v>-0.5405</v>
       </c>
       <c r="P5" t="n">
-        <v>0.3907</v>
+        <v>2.5395</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.3674</v>
+        <v>2.5395</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.7875</v>
+        <v>-0.5433</v>
       </c>
       <c r="T5" t="n">
-        <v>0.7038</v>
+        <v>0.7375</v>
       </c>
       <c r="U5" t="n">
-        <v>-1.4914</v>
+        <v>-1.2809</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.2657</v>
+        <v>-1.8828</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.3321</v>
+        <v>-0.3869</v>
       </c>
       <c r="X5" t="n">
-        <v>0.0664</v>
+        <v>-1.4959</v>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_2484226_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -939,11 +964,16 @@
       <c r="X6" t="n">
         <v>-2.6481</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_2484226_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>V. FERNANDEZ RODRIGUEZ</t>
+          <t>G. GARCIA RIERA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +985,78 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-3.8939</v>
+        <v>-3.2284</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.6239</v>
+        <v>-1.1735</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.27</v>
+        <v>-2.0549</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.63</v>
+        <v>-2.5659</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.5892</v>
+        <v>-0.9739</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.0409</v>
+        <v>-1.592</v>
       </c>
       <c r="J7" t="n">
-        <v>0.4325</v>
+        <v>-0.5686</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.2021</v>
+        <v>0.6178</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6346000000000001</v>
+        <v>-1.1863</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.0625</v>
+        <v>-1.9973</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.387</v>
+        <v>-1.5917</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.6755</v>
+        <v>-0.4056</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.5627</v>
+        <v>0.3907</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.9301</v>
+        <v>-0.9767</v>
       </c>
       <c r="R7" t="n">
         <v>1.3674</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.322</v>
+        <v>-0.7875</v>
       </c>
       <c r="T7" t="n">
-        <v>0.3193</v>
+        <v>0.7038</v>
       </c>
       <c r="U7" t="n">
-        <v>-1.6413</v>
+        <v>-1.4914</v>
       </c>
       <c r="V7" t="n">
-        <v>0.6209</v>
+        <v>-0.2657</v>
       </c>
       <c r="W7" t="n">
-        <v>0.5545</v>
+        <v>-0.3321</v>
       </c>
       <c r="X7" t="n">
         <v>0.0664</v>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_2484226_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. HERNANDEZ GIMENEZ</t>
+          <t>V. FERNANDEZ RODRIGUEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1068,78 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-4.3265</v>
+        <v>-3.8939</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.9166</v>
+        <v>-1.6239</v>
       </c>
       <c r="F8" t="n">
-        <v>-3.4099</v>
+        <v>-2.27</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.7545</v>
+        <v>-1.63</v>
       </c>
       <c r="H8" t="n">
-        <v>0.5104</v>
+        <v>-1.5892</v>
       </c>
       <c r="I8" t="n">
-        <v>-2.2649</v>
+        <v>-0.0409</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.1015</v>
+        <v>0.4325</v>
       </c>
       <c r="K8" t="n">
-        <v>1.3533</v>
+        <v>-0.2021</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.4548</v>
+        <v>0.6346000000000001</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.653</v>
+        <v>-2.0625</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.8429</v>
+        <v>-1.387</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.8101</v>
+        <v>-0.6755</v>
       </c>
       <c r="P8" t="n">
-        <v>-4.1022</v>
+        <v>-1.5627</v>
       </c>
       <c r="Q8" t="n">
-        <v>-5.8603</v>
+        <v>-2.9301</v>
       </c>
       <c r="R8" t="n">
-        <v>1.7581</v>
+        <v>1.3674</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.3055</v>
+        <v>-1.322</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1707</v>
+        <v>0.3193</v>
       </c>
       <c r="U8" t="n">
-        <v>-1.4762</v>
+        <v>-1.6413</v>
       </c>
       <c r="V8" t="n">
-        <v>2.8358</v>
+        <v>0.6209</v>
       </c>
       <c r="W8" t="n">
-        <v>4.8745</v>
+        <v>0.5545</v>
       </c>
       <c r="X8" t="n">
-        <v>-2.0388</v>
+        <v>0.0664</v>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_2484226_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>J. HERNANDEZ GIMENEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,151 +1151,157 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-10.8273</v>
+        <v>-4.3265</v>
       </c>
       <c r="E9" t="n">
-        <v>1.5854</v>
+        <v>-0.9166</v>
       </c>
       <c r="F9" t="n">
-        <v>-12.4128</v>
+        <v>-3.4099</v>
       </c>
       <c r="G9" t="n">
-        <v>-8.1629</v>
+        <v>-1.7545</v>
       </c>
       <c r="H9" t="n">
-        <v>-5.4656</v>
+        <v>0.5104</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.6974</v>
+        <v>-2.2649</v>
       </c>
       <c r="J9" t="n">
-        <v>3.2467</v>
+        <v>-0.1015</v>
       </c>
       <c r="K9" t="n">
-        <v>3.2399</v>
+        <v>1.3533</v>
       </c>
       <c r="L9" t="n">
-        <v>0.006799999999999917</v>
+        <v>-1.4548</v>
       </c>
       <c r="M9" t="n">
-        <v>-11.4096</v>
+        <v>-1.653</v>
       </c>
       <c r="N9" t="n">
-        <v>-8.705399999999999</v>
+        <v>-0.8429</v>
       </c>
       <c r="O9" t="n">
-        <v>-2.7042</v>
+        <v>-0.8101</v>
       </c>
       <c r="P9" t="n">
-        <v>0.976799999999999</v>
+        <v>-4.1022</v>
       </c>
       <c r="Q9" t="n">
-        <v>-12.6972</v>
+        <v>-5.8603</v>
       </c>
       <c r="R9" t="n">
-        <v>13.674</v>
+        <v>1.7581</v>
       </c>
       <c r="S9" t="n">
-        <v>-4.1406</v>
+        <v>-1.3055</v>
       </c>
       <c r="T9" t="n">
-        <v>4.939800000000001</v>
+        <v>0.1707</v>
       </c>
       <c r="U9" t="n">
-        <v>-9.080500000000001</v>
+        <v>-1.4762</v>
       </c>
       <c r="V9" t="n">
-        <v>0.4996</v>
+        <v>2.8358</v>
       </c>
       <c r="W9" t="n">
-        <v>6.096200000000001</v>
+        <v>4.8745</v>
       </c>
       <c r="X9" t="n">
-        <v>-5.5967</v>
+        <v>-2.0388</v>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_2484226_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>P. MARTINEZ ALEJANO</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>C.B. VIC - UNIVERSITAT DE VIC</t>
+          <t>SA TINTINA CB ES CASTELL MENORCA</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>9.8499</v>
+        <v>-10.8273</v>
       </c>
       <c r="E10" t="n">
-        <v>9.7836</v>
+        <v>1.5854</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0663</v>
+        <v>-12.4128</v>
       </c>
       <c r="G10" t="n">
-        <v>10.0188</v>
+        <v>-8.1629</v>
       </c>
       <c r="H10" t="n">
-        <v>2.9916</v>
+        <v>-5.4656</v>
       </c>
       <c r="I10" t="n">
-        <v>7.0272</v>
+        <v>-2.6974</v>
       </c>
       <c r="J10" t="n">
-        <v>9.8439</v>
+        <v>3.2467</v>
       </c>
       <c r="K10" t="n">
-        <v>3.625</v>
+        <v>3.2399</v>
       </c>
       <c r="L10" t="n">
-        <v>6.2189</v>
+        <v>0.006899999999999906</v>
       </c>
       <c r="M10" t="n">
-        <v>0.1749</v>
+        <v>-11.4096</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.6334</v>
+        <v>-8.705399999999999</v>
       </c>
       <c r="O10" t="n">
-        <v>0.8083</v>
+        <v>-2.7042</v>
       </c>
       <c r="P10" t="n">
-        <v>0.7814</v>
+        <v>0.9768000000000008</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.9767</v>
+        <v>-12.6972</v>
       </c>
       <c r="R10" t="n">
-        <v>1.7581</v>
+        <v>13.674</v>
       </c>
       <c r="S10" t="n">
-        <v>0.6004</v>
+        <v>-4.140600000000001</v>
       </c>
       <c r="T10" t="n">
-        <v>1.2485</v>
+        <v>4.9398</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.6481</v>
+        <v>-9.080500000000001</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.5507</v>
+        <v>0.4996</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.3321</v>
+        <v>6.096200000000001</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.2186</v>
-      </c>
+        <v>-5.5967</v>
+      </c>
+      <c r="Y10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>D. NGUBA ETAME</t>
+          <t>P. MARTINEZ ALEJANO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1313,78 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>6.1133</v>
+        <v>9.8499</v>
       </c>
       <c r="E11" t="n">
-        <v>5.7742</v>
+        <v>9.7836</v>
       </c>
       <c r="F11" t="n">
-        <v>0.3392</v>
+        <v>0.0663</v>
       </c>
       <c r="G11" t="n">
-        <v>3.4634</v>
+        <v>10.0188</v>
       </c>
       <c r="H11" t="n">
-        <v>3.0867</v>
+        <v>2.9916</v>
       </c>
       <c r="I11" t="n">
-        <v>0.3766</v>
+        <v>7.0272</v>
       </c>
       <c r="J11" t="n">
-        <v>4.0929</v>
+        <v>9.8439</v>
       </c>
       <c r="K11" t="n">
-        <v>3.8501</v>
+        <v>3.625</v>
       </c>
       <c r="L11" t="n">
-        <v>0.2428</v>
+        <v>6.2189</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.6294999999999999</v>
+        <v>0.1749</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.7634</v>
+        <v>-0.6334</v>
       </c>
       <c r="O11" t="n">
-        <v>0.1338</v>
+        <v>0.8083</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.3907</v>
+        <v>0.7814</v>
       </c>
       <c r="Q11" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R11" t="n">
-        <v>0.586</v>
+        <v>1.7581</v>
       </c>
       <c r="S11" t="n">
-        <v>2.3765</v>
+        <v>0.6004</v>
       </c>
       <c r="T11" t="n">
-        <v>2.3807</v>
+        <v>1.2485</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0043</v>
+        <v>-0.6481</v>
       </c>
       <c r="V11" t="n">
-        <v>0.6642</v>
+        <v>-1.5507</v>
       </c>
       <c r="W11" t="n">
-        <v>0.2772</v>
+        <v>-0.3321</v>
       </c>
       <c r="X11" t="n">
-        <v>0.3869</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_2484226_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>D. VIDAL TEIXIDOR</t>
+          <t>D. NGUBA ETAME</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1396,78 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>2.9032</v>
+        <v>6.1133</v>
       </c>
       <c r="E12" t="n">
-        <v>3.6569</v>
+        <v>5.7742</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.7537</v>
+        <v>0.3392</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.353</v>
+        <v>3.4634</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.4213</v>
+        <v>3.0867</v>
       </c>
       <c r="I12" t="n">
-        <v>0.0683</v>
+        <v>0.3766</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.0533</v>
+        <v>4.0929</v>
       </c>
       <c r="K12" t="n">
-        <v>0.1471</v>
+        <v>3.8501</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.2004</v>
+        <v>0.2428</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.2998</v>
+        <v>-0.6294999999999999</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.5684</v>
+        <v>-0.7634</v>
       </c>
       <c r="O12" t="n">
-        <v>0.2687</v>
+        <v>0.1338</v>
       </c>
       <c r="P12" t="n">
-        <v>1.7581</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R12" t="n">
-        <v>1.7581</v>
+        <v>0.586</v>
       </c>
       <c r="S12" t="n">
-        <v>0.6665</v>
+        <v>2.3765</v>
       </c>
       <c r="T12" t="n">
-        <v>1.6599</v>
+        <v>2.3807</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.9933999999999999</v>
+        <v>-0.0043</v>
       </c>
       <c r="V12" t="n">
-        <v>0.8317</v>
+        <v>0.6642</v>
       </c>
       <c r="W12" t="n">
-        <v>2.0503</v>
+        <v>0.2772</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.2186</v>
+        <v>0.3869</v>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_2484226_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A. SIMON</t>
+          <t>D. VIDAL TEIXIDOR</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1479,78 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>1.661</v>
+        <v>2.9032</v>
       </c>
       <c r="E13" t="n">
-        <v>1.993</v>
+        <v>3.6569</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.332</v>
+        <v>-0.7537</v>
       </c>
       <c r="G13" t="n">
-        <v>0.2981</v>
+        <v>-0.353</v>
       </c>
       <c r="H13" t="n">
-        <v>1.0269</v>
+        <v>-0.4213</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.7288</v>
+        <v>0.0683</v>
       </c>
       <c r="J13" t="n">
-        <v>0.9375</v>
+        <v>-0.0533</v>
       </c>
       <c r="K13" t="n">
-        <v>1.3955</v>
+        <v>0.1471</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.458</v>
+        <v>-0.2004</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.6394</v>
+        <v>-0.2998</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.3686</v>
+        <v>-0.5684</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.2708</v>
+        <v>0.2687</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.7814</v>
+        <v>1.7581</v>
       </c>
       <c r="Q13" t="n">
-        <v>-2.9301</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>2.1488</v>
+        <v>1.7581</v>
       </c>
       <c r="S13" t="n">
-        <v>0.5935</v>
+        <v>0.6665</v>
       </c>
       <c r="T13" t="n">
-        <v>0.9389999999999999</v>
+        <v>1.6599</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.3455</v>
+        <v>-0.9933999999999999</v>
       </c>
       <c r="V13" t="n">
-        <v>1.5507</v>
+        <v>0.8317</v>
       </c>
       <c r="W13" t="n">
-        <v>3.0466</v>
+        <v>2.0503</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.4959</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_2484226_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>C. VIDAL AGRA</t>
+          <t>A. SIMON</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1562,78 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.8826000000000001</v>
+        <v>1.661</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.4566</v>
+        <v>1.993</v>
       </c>
       <c r="F14" t="n">
-        <v>1.3392</v>
+        <v>-0.332</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.1235</v>
+        <v>0.2981</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.2985</v>
+        <v>1.0269</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1751</v>
+        <v>-0.7288</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.2435</v>
+        <v>0.9375</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.284</v>
+        <v>1.3955</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0405</v>
+        <v>-0.458</v>
       </c>
       <c r="M14" t="n">
-        <v>0.1201</v>
+        <v>-0.6394</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.0146</v>
+        <v>-0.3686</v>
       </c>
       <c r="O14" t="n">
-        <v>0.1346</v>
+        <v>-0.2708</v>
       </c>
       <c r="P14" t="n">
-        <v>0.586</v>
+        <v>-0.7814</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.9767</v>
+        <v>-2.9301</v>
       </c>
       <c r="R14" t="n">
-        <v>1.5627</v>
+        <v>2.1488</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.2442</v>
+        <v>0.5935</v>
       </c>
       <c r="T14" t="n">
-        <v>0.4864</v>
+        <v>0.9389999999999999</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.7306</v>
+        <v>-0.3455</v>
       </c>
       <c r="V14" t="n">
-        <v>0.6642</v>
+        <v>1.5507</v>
       </c>
       <c r="W14" t="n">
-        <v>0.2772</v>
+        <v>3.0466</v>
       </c>
       <c r="X14" t="n">
-        <v>0.3869</v>
+        <v>-1.4959</v>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_2484226_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>À. RIERA PERETÓ</t>
+          <t>C. VIDAL AGRA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,40 +1645,40 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0572</v>
+        <v>0.8826000000000001</v>
       </c>
       <c r="E15" t="n">
-        <v>-1.0327</v>
+        <v>-0.4566</v>
       </c>
       <c r="F15" t="n">
-        <v>1.0899</v>
+        <v>1.3392</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.7752</v>
+        <v>-0.1235</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.5054999999999999</v>
+        <v>-0.2985</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.2696</v>
+        <v>0.1751</v>
       </c>
       <c r="J15" t="n">
-        <v>-1.4944</v>
+        <v>-0.2435</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.2814</v>
+        <v>-0.284</v>
       </c>
       <c r="L15" t="n">
-        <v>-1.213</v>
+        <v>0.0405</v>
       </c>
       <c r="M15" t="n">
-        <v>0.7193000000000001</v>
+        <v>0.1201</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.2241</v>
+        <v>-0.0146</v>
       </c>
       <c r="O15" t="n">
-        <v>0.9433</v>
+        <v>0.1346</v>
       </c>
       <c r="P15" t="n">
         <v>0.586</v>
@@ -1624,28 +1690,33 @@
         <v>1.5627</v>
       </c>
       <c r="S15" t="n">
-        <v>0.8557</v>
+        <v>-0.2442</v>
       </c>
       <c r="T15" t="n">
-        <v>1.1612</v>
+        <v>0.4864</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.3055</v>
+        <v>-0.7306</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.6093</v>
+        <v>0.6642</v>
       </c>
       <c r="W15" t="n">
         <v>0.2772</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.8865</v>
+        <v>0.3869</v>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_2484226_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. LAJAY BOBEPARI</t>
+          <t>À. RIERA PERETÓ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1728,78 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.0393</v>
+        <v>0.607</v>
       </c>
       <c r="E16" t="n">
-        <v>0.0764</v>
+        <v>0.607</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.1157</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0.738</v>
+        <v>0.607</v>
       </c>
       <c r="H16" t="n">
-        <v>1.1292</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.3912</v>
+        <v>0.607</v>
       </c>
       <c r="J16" t="n">
-        <v>1.0179</v>
+        <v>0.607</v>
       </c>
       <c r="K16" t="n">
-        <v>1.0041</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0138</v>
+        <v>0.607</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.2799</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>0.1251</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.4051</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.5627</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0.3907</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>1.0627</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>1.0119</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0508</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_2484226_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>F. PALLARES ARUMI</t>
+          <t>A. LAJAY BOBEPARI</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1811,78 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.1824</v>
+        <v>-0.0393</v>
       </c>
       <c r="E17" t="n">
-        <v>0.5995</v>
+        <v>0.0764</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.7818000000000001</v>
+        <v>-0.1157</v>
       </c>
       <c r="G17" t="n">
-        <v>1.1285</v>
+        <v>0.738</v>
       </c>
       <c r="H17" t="n">
-        <v>1.1822</v>
+        <v>1.1292</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.0537</v>
+        <v>-0.3912</v>
       </c>
       <c r="J17" t="n">
-        <v>1.2782</v>
+        <v>1.0179</v>
       </c>
       <c r="K17" t="n">
-        <v>1.3315</v>
+        <v>1.0041</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.0533</v>
+        <v>0.0138</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.1498</v>
+        <v>-0.2799</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.1494</v>
+        <v>0.1251</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.0004</v>
+        <v>-0.4051</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.1953</v>
+        <v>-1.5627</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9767</v>
+        <v>-1.9534</v>
       </c>
       <c r="R17" t="n">
-        <v>0.7814</v>
+        <v>0.3907</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3804</v>
+        <v>1.0627</v>
       </c>
       <c r="T17" t="n">
-        <v>0.2979</v>
+        <v>1.0119</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0824</v>
+        <v>0.0508</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.4959</v>
+        <v>-0.2772</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.4959</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_2484226_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>O. SUBIRANAS CASELLAS</t>
+          <t>F. PALLARES ARUMI</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1894,78 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-3.7049</v>
+        <v>-0.1824</v>
       </c>
       <c r="E18" t="n">
-        <v>-3.0076</v>
+        <v>0.5995</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.6973</v>
+        <v>-0.7818000000000001</v>
       </c>
       <c r="G18" t="n">
-        <v>-2.6917</v>
+        <v>1.1285</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.4375</v>
+        <v>1.1822</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.2542</v>
+        <v>-0.0537</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.0488</v>
+        <v>1.2782</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.4694</v>
+        <v>1.3315</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.5794</v>
+        <v>-0.0533</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.6429</v>
+        <v>-0.1498</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.968</v>
+        <v>-0.1494</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.6749000000000001</v>
+        <v>-0.0004</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.586</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.9534</v>
+        <v>-0.9767</v>
       </c>
       <c r="R18" t="n">
-        <v>1.3674</v>
+        <v>0.7814</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.15</v>
+        <v>0.3804</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.0054</v>
+        <v>0.2979</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1445</v>
+        <v>0.0824</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.2772</v>
+        <v>-1.4959</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.2772</v>
+        <v>-1.4959</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_2484226_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. CRUZ URBANEJA</t>
+          <t>A. RIERA PERETO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1977,78 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-4.7599</v>
+        <v>-0.5498</v>
       </c>
       <c r="E19" t="n">
-        <v>-4.9738</v>
+        <v>-1.6397</v>
       </c>
       <c r="F19" t="n">
-        <v>0.2139</v>
+        <v>1.0899</v>
       </c>
       <c r="G19" t="n">
-        <v>-3.5403</v>
+        <v>-1.3821</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.2881</v>
+        <v>-0.5054999999999999</v>
       </c>
       <c r="I19" t="n">
-        <v>-2.2523</v>
+        <v>-0.8766</v>
       </c>
       <c r="J19" t="n">
-        <v>-2.9207</v>
+        <v>-2.1014</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.613</v>
+        <v>-0.2814</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.3077</v>
+        <v>-1.82</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.6196</v>
+        <v>0.7193000000000001</v>
       </c>
       <c r="N19" t="n">
-        <v>0.3249</v>
+        <v>-0.2241</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.9445</v>
+        <v>0.9433</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.1721</v>
+        <v>0.586</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.9534</v>
+        <v>-0.9767</v>
       </c>
       <c r="R19" t="n">
-        <v>0.7814</v>
+        <v>1.5627</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.0475</v>
+        <v>0.8557</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.0997</v>
+        <v>1.1612</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0522</v>
+        <v>-0.3055</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>-0.6093</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-0.8865</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_2484226_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>O. SUBIRANAS CASELLAS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,68 +2060,235 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
+        <v>-3.7049</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-3.0076</v>
+      </c>
+      <c r="F20" t="n">
+        <v>-0.6973</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-2.6917</v>
+      </c>
+      <c r="H20" t="n">
+        <v>-1.4375</v>
+      </c>
+      <c r="I20" t="n">
+        <v>-1.2542</v>
+      </c>
+      <c r="J20" t="n">
+        <v>-1.0488</v>
+      </c>
+      <c r="K20" t="n">
+        <v>-0.4694</v>
+      </c>
+      <c r="L20" t="n">
+        <v>-0.5794</v>
+      </c>
+      <c r="M20" t="n">
+        <v>-1.6429</v>
+      </c>
+      <c r="N20" t="n">
+        <v>-0.968</v>
+      </c>
+      <c r="O20" t="n">
+        <v>-0.6749000000000001</v>
+      </c>
+      <c r="P20" t="n">
+        <v>-0.586</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>-1.9534</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.3674</v>
+      </c>
+      <c r="S20" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="T20" t="n">
+        <v>-0.0054</v>
+      </c>
+      <c r="U20" t="n">
+        <v>-0.1445</v>
+      </c>
+      <c r="V20" t="n">
+        <v>-0.2772</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0</v>
+      </c>
+      <c r="X20" t="n">
+        <v>-0.2772</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_2484226_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>M. CRUZ URBANEJA</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>C.B. VIC - UNIVERSITAT DE VIC</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" t="n">
+        <v>-4.7599</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-4.9738</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.2139</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-3.5403</v>
+      </c>
+      <c r="H21" t="n">
+        <v>-1.2881</v>
+      </c>
+      <c r="I21" t="n">
+        <v>-2.2523</v>
+      </c>
+      <c r="J21" t="n">
+        <v>-2.9207</v>
+      </c>
+      <c r="K21" t="n">
+        <v>-1.613</v>
+      </c>
+      <c r="L21" t="n">
+        <v>-1.3077</v>
+      </c>
+      <c r="M21" t="n">
+        <v>-0.6196</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0.3249</v>
+      </c>
+      <c r="O21" t="n">
+        <v>-0.9445</v>
+      </c>
+      <c r="P21" t="n">
+        <v>-1.1721</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>-1.9534</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0.7814</v>
+      </c>
+      <c r="S21" t="n">
+        <v>-0.0475</v>
+      </c>
+      <c r="T21" t="n">
+        <v>-0.0997</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0.0522</v>
+      </c>
+      <c r="V21" t="n">
+        <v>0</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0</v>
+      </c>
+      <c r="X21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_2484226_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>--- TOTAL ---</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>C.B. VIC - UNIVERSITAT DE VIC</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" t="n">
         <v>12.7807</v>
       </c>
-      <c r="E20" t="n">
+      <c r="E22" t="n">
         <v>12.4129</v>
       </c>
-      <c r="F20" t="n">
-        <v>0.3679999999999999</v>
-      </c>
-      <c r="G20" t="n">
-        <v>8.163100000000002</v>
-      </c>
-      <c r="H20" t="n">
+      <c r="F22" t="n">
+        <v>0.3679999999999998</v>
+      </c>
+      <c r="G22" t="n">
+        <v>8.163200000000002</v>
+      </c>
+      <c r="H22" t="n">
         <v>5.4657</v>
       </c>
-      <c r="I20" t="n">
+      <c r="I22" t="n">
         <v>2.6974</v>
       </c>
-      <c r="J20" t="n">
+      <c r="J22" t="n">
         <v>11.4097</v>
       </c>
-      <c r="K20" t="n">
+      <c r="K22" t="n">
         <v>8.705500000000001</v>
       </c>
-      <c r="L20" t="n">
+      <c r="L22" t="n">
         <v>2.704199999999999</v>
       </c>
-      <c r="M20" t="n">
+      <c r="M22" t="n">
         <v>-3.2466</v>
       </c>
-      <c r="N20" t="n">
+      <c r="N22" t="n">
         <v>-3.2399</v>
       </c>
-      <c r="O20" t="n">
+      <c r="O22" t="n">
         <v>-0.007000000000000006</v>
       </c>
-      <c r="P20" t="n">
-        <v>-0.9767</v>
-      </c>
-      <c r="Q20" t="n">
+      <c r="P22" t="n">
+        <v>-0.9767000000000001</v>
+      </c>
+      <c r="Q22" t="n">
         <v>-13.6738</v>
       </c>
-      <c r="R20" t="n">
+      <c r="R22" t="n">
         <v>12.6973</v>
       </c>
-      <c r="S20" t="n">
-        <v>6.094</v>
-      </c>
-      <c r="T20" t="n">
-        <v>9.080399999999999</v>
-      </c>
-      <c r="U20" t="n">
+      <c r="S22" t="n">
+        <v>6.093999999999999</v>
+      </c>
+      <c r="T22" t="n">
+        <v>9.080400000000001</v>
+      </c>
+      <c r="U22" t="n">
         <v>-2.986499999999999</v>
       </c>
-      <c r="V20" t="n">
-        <v>-0.4994999999999997</v>
-      </c>
-      <c r="W20" t="n">
-        <v>5.5964</v>
-      </c>
-      <c r="X20" t="n">
+      <c r="V22" t="n">
+        <v>-0.4994999999999995</v>
+      </c>
+      <c r="W22" t="n">
+        <v>5.596399999999999</v>
+      </c>
+      <c r="X22" t="n">
         <v>-6.096099999999999</v>
       </c>
+      <c r="Y22" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
